--- a/PopulationCalculationData.xlsx
+++ b/PopulationCalculationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Filipe\FODD\Scripts\PopulationCalculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1CE942-F986-4724-B24A-4BC77C25993F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB99F6CA-5C5F-4450-A764-D68C191C6AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,6 +500,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
